--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -655,7 +655,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  时间        2026-09-24 16:59:16</t>
+          <t xml:space="preserve">  时间        2026-09-27 13:10:03</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  命令      excel-codegen render -c examples\example.yaml -x examples\template.xlsx --write-excel --outdir examples\generated</t>
+          <t xml:space="preserve">  命令      excel-codegen render -c examples/example.yaml -x examples/template.xlsx --write-excel --outdir examples/generated</t>
         </is>
       </c>
     </row>
@@ -808,6 +808,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="取值不合规" error="baud：范围: 300 ~ 4000000" promptTitle="baud" prompt="范围: 300 ~ 4000000" type="whole" operator="between">
+      <formula1>300</formula1>
+      <formula2>4000000</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -901,7 +907,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>模式</t>
+          <t>模式（取值约束：Excel 里会变成下拉列表）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -921,6 +927,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E3 F3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="取值不合规" error="mode：可选: TX / RX / TX_RX" promptTitle="mode" prompt="可选: TX / RX / TX_RX" type="list">
+      <formula1>"TX,RX,TX_RX"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1413,7 +1424,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-24 16:59:16</t>
+          <t>2026-09-27 13:10:03</t>
         </is>
       </c>
     </row>

--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -655,7 +655,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  时间        2026-09-27 13:10:03</t>
+          <t xml:space="preserve">  时间        2026-09-27 15:04:12</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-27 13:10:03</t>
+          <t>2026-09-27 15:04:12</t>
         </is>
       </c>
     </row>

--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -231,6 +231,78 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel_codegen</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>波特率
+填写位置：Global 表 B 列（所有 Case 共用）
+单位：bps
+类型：int
+约束：范围: 300 ~ 4000000
+默认值：115200
+模板里引用：{{ baud }}</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>分频值 = baud / 16（派生参数：引用另一个参数，不用手填）
+自动计算：baud / 16
+不用手填；改了它引用的输入后会自动重算。
+类型：float
+模板里引用：{{ baud_div }}</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>MCU 型号（字符串变量示例）
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：auto
+约束：格式: ^STM32[A-Z][0-9]{3}[A-Z]{0,2}$
+默认值：STM32F103
+模板里引用：{{ mcu }}</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel_codegen</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>端口
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：auto
+约束：格式: ^[A-H]$
+前缀 / 后缀：'GPIO' / '_PORT'
+默认值：A
+模板里引用：{{ port }}</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>模式（取值约束：Excel 里会变成下拉列表）
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：auto
+约束：可选: TX / RX / TX_RX
+前缀 / 后缀：'MODE_' / ''
+默认值：TX_RX
+模板里引用：{{ mode }}</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -655,7 +727,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  时间        2026-09-27 15:04:12</t>
+          <t xml:space="preserve">  时间        2026-09-27 15:06:33</t>
         </is>
       </c>
     </row>
@@ -815,6 +887,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -933,6 +1006,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1424,7 +1498,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-27 15:04:12</t>
+          <t>2026-09-27 15:06:33</t>
         </is>
       </c>
     </row>

--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -655,129 +655,136 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">      ★ 懒得开终端就双击本文件旁边的 template_render.bat（Windows）或跑 template_render.sh（Linux / macOS）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>⚠  部分输出表是「快照」，不是活公式</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   在 Excel 里改了参数、但没跑上面那条命令，输出表里的代码还是上一次的。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">   在 Excel 里改了参数、但没跑上面那条命令，输出表里的代码还是上一次的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">   不带 --write-excel 的 render 只预览，不会改变本文件。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>输出位置</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  uart_init: Output @ B2 (horizontal)［快照·需重跑］</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
+          <t xml:space="preserve">  uart_init: Output @ B2 (horizontal)［快照·需重跑］</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
           <t xml:space="preserve">  uart_summary: Output Vertical @ B2 (vertical)［快照·需重跑］</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Template（隐藏）：模板原文，只读参考，改它不影响渲染结果。</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>本次生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  时间        2026-09-27 15:06:33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  输出指纹      def6202499b3</t>
+          <t xml:space="preserve">  时间        2026-09-27 15:09:11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  参数指纹      ef98e96a376d</t>
+          <t xml:space="preserve">  输出指纹      def6202499b3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  case 数    2</t>
+          <t xml:space="preserve">  参数指纹      ef98e96a376d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  case 数    2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">  cases     Case1, Case2</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  命令      excel-codegen render -c examples/example.yaml -x examples/template.xlsx --write-excel --outdir examples/generated</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>工况一览（来自上一次渲染）</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Case1, Case2</t>
         </is>
@@ -1498,7 +1505,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-27 15:06:33</t>
+          <t>2026-09-27 15:09:11</t>
         </is>
       </c>
     </row>

--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -734,7 +734,7 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  时间        2026-09-27 15:09:11</t>
+          <t xml:space="preserve">  时间        2026-09-27 15:23:10</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-27 15:09:11</t>
+          <t>2026-09-27 15:23:10</t>
         </is>
       </c>
     </row>
